--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_14-11-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_14-11-2025.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>£9.74</t>
+          <t>£9.72</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>£9.83</t>
+          <t>£10.25</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>£11.40</t>
+          <t>Error: 'NoneType' object has no attribute 'find'</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'find'</t>
+          <t>£25.68</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'find'</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
